--- a/data_extactor/batch_10_fa/batch_0073_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0073_fa.xlsx
@@ -513,22 +513,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | طراحی | ریاضیات | زبان انگلیسی | امور اداری و مدیریت | خدمات مشتریان و پرسنل | شیمی | مکانیک | ایمنی و امنیت عمومی</t>
+          <t>ساختمان و ساخت‌وساز | طراحی | ریاضیات | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | شیمی | مکانیک | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>چالاکی دست | بینایی نزدیک | قدرت بالاتنه | هماهنگی میان‌اندازه‌ای | ثبات دست و بازو | بینایی دور | چالاکی انگشتان | انعطاف‌پذیری کششی | استقامت بدنی | قدرت ایستا | دقت کنترل | تجسم فضایی | حساسیت به مشکلات | تشخیص رنگ‌های بصری | قدرت پویا | توجه انتخابی | ترتیب‌دهی به اطلاعات</t>
+          <t>مهارت دستی | بینایی نزدیک | قدرت تنه | هماهنگی چند عضو | ثبات دست و بازو | بینایی دور | مهارت انگشتان | انعطاف‌پذیری دامنه حرکت | استقامت | قدرت ایستا | دقت کنترل | تجسم | حساسیت به مسئله | تشخیص رنگ بصری | قدرت پویا | توجه انتخابی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان به صورت ایستاده | کار با یا مشارکت در یک گروه یا تیم کاری | اهمیت دقیق یا درست بودن کار | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض آلاینده‌ها | سلامت و ایمنی سایر کارگران | صرف زمان به صورت زانو زده، چمباتمه زده، خمیده یا خزیده | صرف زمان برای خم کردن یا چرخاندن بدن | پیامدهای کاری و نتایج سایر کارگران | نزدیکی فیزیکی | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای ایستادن | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض آلاینده‌ها | سلامت و ایمنی سایر کارکنان | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای خم کردن یا چرخاندن بدن | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>بناهای آجر و بلوک | نجاران | نصابان موکت | سیمان‌کاران و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | کف‌سازان، به جز موکت، چوب و کاشی‌های سخت | ساب‌زن‌ها و پرداخت‌کاران کف | قالب‌سازان و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران مبلمان | کارگران ساب‌زنی و صیقل‌کاری دستی | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | گچ‌کاران و سیمان‌کاران نما | تعمیرکاران مواد نسوز، به جز بناهای آجر | سنگ‌فرش‌کاران قطعه‌ای | برش‌دهندگان و تراش‌دهندگان سنگ، تولیدی | سنگ‌تراشان | نصابان کاشی و سنگ</t>
+          <t>بنّایان آجرکار و بلوک‌کار | نجّاران | نصّابان موکت و فرش | بنّایان سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | سنباده‌کاران و پرداخت‌کاران کف | قالب‌سازان و ماهیچه‌سازان کارگاه ریخته‌گری | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پرداخت دستی | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | گچ‌کاران و بناهای سیمان‌کاری | تعمیرکاران مواد نسوز، به جز بناهای آجرکار | سنگ‌فرش‌کاران قطعه‌ای | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | بنّایان سنگ‌کار | کاشی‌کاران و سنگ‌کاران</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -575,17 +575,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>چالاکی دست | قدرت ایستا | هماهنگی میان‌اندازه‌ای | ثبات دست و بازو | درک شفاهی | بیان شفاهی | حساسیت به مشکلات | دقت کنترل | قدرت بالاتنه | بینایی نزدیک | بینایی دور | انعطاف‌پذیری کششی | استقامت بدنی | قدرت پویا | چالاکی انگشتان | ترتیب‌دهی به اطلاعات | وضوح گفتار | تشخیص گفتار | درک عمق | کنترل سرعت | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی</t>
+          <t>مهارت دستی | قدرت ایستا | هماهنگی چند عضو | ثبات دست و بازو | درک شفاهی | بیان شفاهی | حساسیت به مسئله | دقت کنترل | قدرت تنه | بینایی نزدیک | بینایی دور | انعطاف‌پذیری دامنه حرکت | استقامت | قدرت پویا | مهارت انگشتان | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | درک عمق | کنترل نرخ | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان به صورت ایستاده | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | ارتباط با دیگران | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض تجهیزات خطرناک | مکالمات تلفنی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه یا تیم کاری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فشار زمانی | تعداد دفعات تصمیم‌گیری | پیامد اشتباهات | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن کار | سلامت و ایمنی سایر کارگران | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | نزدیکی فیزیکی</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای ایستادن | فضای باز، در معرض تمام شرایط آب و هوایی | ارتباط با دیگران | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض تجهیزات خطرناک | مکالمات تلفنی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فشار زمانی | فراوانی تصمیم‌گیری | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>بناهای آجر و بلوک | نجاران | سیمان‌کاران و پرداخت‌کاران بتن | نصابان دیوار خشک و تایل سقف | اپراتورهای ماشین‌های حفاری و بارگیری و دراگ‌لاین، معدن‌کاری سطحی | کارگران ساب‌زنی و صیقل‌کاری دستی | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | اپراتورهای بالابر و وینچ | کارگران عایق‌کاری کف، سقف و دیوار | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تعمیرکاران ماشین‌آلات | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای تجهیزات روسازی، زیرسازی و کوبش | لوله‌گذاران | لوله‌کش‌ها، نصابان لوله و لوله‌کش‌های بخار | سنگ‌فرش‌کاران قطعه‌ای | کارگران ورق‌کاری فلزی | کارگران اسکلت فلزی و فولادی ساختمانی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب، به جز اره‌کشی</t>
+          <t>بنّایان آجرکار و بلوک‌کار | نجّاران | بنّایان سیمان‌کار و پرداخت‌کاران بتن | نصابان دیوار خشک و تایل سقف | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | کارگران سنگ‌زنی و پرداخت دستی | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | اپراتورهای بالابر و وینچ | کارگران عایق‌کاری کف، سقف و دیوار | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای تجهیزات روسازی، زیرسازی و کوبش | لوله‌گذاران | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | سنگ‌فرش‌کاران قطعه‌ای | کارگران ورق‌کاری | کارگران سازه‌های آهنی و فولادی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>دقت کنترل | حساسیت به مشکلات | هماهنگی میان‌اندازه‌ای | کنترل سرعت | زمان عکس‌العمل | بینایی دور | قدرت بالاتنه | قدرت ایستا | وضوح گفتار | تشخیص گفتار | درک عمق | ثبات دست و بازو | توجه انتخابی | تجسم فضایی | ترتیب‌دهی به اطلاعات | استدلال قیاسی | بیان شفاهی | درک شفاهی | انعطاف‌پذیری کششی | جهت‌گیری پاسخ | چالاکی دست</t>
+          <t>دقت کنترل | حساسیت به مسئله | هماهنگی چند عضو | کنترل نرخ | زمان عکس‌العمل | بینایی دور | قدرت تنه | قدرت ایستا | وضوح گفتار | تشخیص گفتار | درک عمق | ثبات دست و بازو | توجه انتخابی | تجسم | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان شفاهی | درک شفاهی | انعطاف‌پذیری دامنه حرکت | جهت‌گیری پاسخ | مهارت دستی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض ارتعاش کل بدن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | داخل خودروی روباز یا کار با تجهیزات | مکالمات تلفنی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، نیش‌ها یا گزیدگی‌ها | نزدیکی فیزیکی | صرف زمان برای انجام حرکات تکراری | داخل خودروی کابین‌دار یا کار با تجهیزات کابین‌دار | سرعت تعیین‌شده توسط سرعت تجهیزات | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه یا تیم کاری | سلامت و ایمنی سایر کارگران | پیامد اشتباهات | پیامدهای کاری و نتایج سایر کارگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | ارتباط با دیگران</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض ارتعاش کل بدن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | در یک وسیله نقلیه روباز یا کار با تجهیزات | مکالمات تلفنی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | نزدیکی فیزیکی | صرف زمان برای انجام حرکات تکراری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | سرعت تعیین‌شده توسط سرعت تجهیزات | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | پیامد خطا | پیامدهای کاری و نتایج سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | ارتباط با دیگران</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>سیمان‌کاران و پرداخت‌کاران بتن | کارگران ساختمانی | اپراتورهای ماشین‌های استخراج مداوم | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و دراگ‌لاین، معدن‌کاری سطحی | کارگران ساب‌زنی و صیقل‌کاری دستی | کارگران نگهداری بزرگراه‌ها | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | تعمیرکاران ماشین‌آلات | نصب‌کنندگان ماشین‌آلات صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتور | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای کوبنده شمع | لوله‌گذاران | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | کارگران ساده، نفت و گاز | سنگ‌فرش‌کاران قطعه‌ای | کارگران و پرداخت‌کاران ترازو | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب، به جز اره‌کشی</t>
+          <t>بنّایان سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | اپراتورهای ماشین استخراج مداوم | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | کارگران سنگ‌زنی و پرداخت دستی | کارگران نگهداری بزرگراه‌ها | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای کوبنده شمع | لوله‌گذاران | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | کارگران فنی همه‌کاره نفت و گاز | سنگ‌فرش‌کاران قطعه‌ای | کارگران و پرداخت‌کاران ترازو | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -684,22 +684,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | مکانیک | ریاضیات | حمل‌ونقل | مهندسی و فناوری | ایمنی و امنیت عمومی | طراحی</t>
+          <t>ساختمان و ساخت‌وساز | مکانیک | ریاضیات | حمل و نقل | مهندسی و فناوری | ایمنی و امنیت عمومی | طراحی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>دقت کنترل | درک عمق | هماهنگی میان‌اندازه‌ای | زمان عکس‌العمل | چالاکی دست | حساسیت به مشکلات | کنترل سرعت | جهت‌گیری پاسخ | توجه انتخابی | ثبات دست و بازو | استدلال قیاسی | تشخیص گفتار | بینایی دور | تجسم فضایی | توجه شنیداری | بینایی نزدیک | چالاکی انگشتان | جهت‌یابی فضایی | ترتیب‌دهی به اطلاعات | استدلال استقرایی | بیان شفاهی | درک شفاهی</t>
+          <t>دقت کنترل | درک عمق | هماهنگی چند عضو | زمان عکس‌العمل | مهارت دستی | حساسیت به مسئله | کنترل نرخ | جهت‌گیری پاسخ | توجه انتخابی | ثبات دست و بازو | استدلال قیاسی | تشخیص گفتار | بینایی دور | تجسم | توجه شنیداری | بینایی نزدیک | مهارت انگشتان | جهت‌گیری فضایی | ترتیب‌دهی اطلاعات | استدلال استقرایی | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارگران | کار با یا مشارکت در یک گروه یا تیم کاری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | ارتباط با دیگران | قرار گرفتن در معرض تجهیزات خطرناک | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن کار | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعداد دفعات تصمیم‌گیری | پیامد اشتباهات | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | پیامدهای کاری و نتایج سایر کارگران | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | داخل خودروی روباز یا کار با تجهیزات | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض ارتعاش کل بدن | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | ارتباط با دیگران | قرار گرفتن در معرض تجهیزات خطرناک | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | پیامد خطا | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | در یک وسیله نقلیه روباز یا کار با تجهیزات | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض ارتعاش کل بدن | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | کارگران ساختمانی | اپراتورهای ماشین‌های استخراج مداوم | اپراتورهای جرثقیل و تاورکرین | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و دراگ‌لاین، معدن‌کاری سطحی | کارگران نگهداری بزرگراه‌ها | اپراتورهای بالابر و وینچ | اپراتورهای خودروهای صنعتی و تراکتور | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | تعمیرکاران ماشین‌آلات | نصب‌کنندگان ماشین‌آلات صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتور | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای تجهیزات روسازی، زیرسازی و کوبش | تعمیرکاران واگن‌های ریلی | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | دکل‌بندها | کارگران ساده، نفت و گاز | کارگران اسکلت فلزی و فولادی ساختمانی</t>
+          <t>مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | کارگران ساختمانی | اپراتورهای ماشین استخراج مداوم | اپراتورهای جرثقیل و تاور | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | کارگران نگهداری بزرگراه‌ها | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون صنعتی | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای تجهیزات روسازی، زیرسازی و کوبش | تعمیرکنندگان واگن‌های ریلی | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | ریگرها | کارگران فنی همه‌کاره نفت و گاز | کارگران سازه‌های آهنی و فولادی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -746,17 +746,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دقت کنترل | درک عمق | هماهنگی میان‌اندازه‌ای | بینایی نزدیک | بینایی دور | کنترل سرعت | زمان عکس‌العمل | ثبات دست و بازو | جهت‌گیری پاسخ | حساسیت به مشکلات | درک شفاهی | تجسم فضایی | سرعت ادراکی | چالاکی دست | وضوح گفتار | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی | تشخیص رنگ‌های بصری | قدرت ایستا | چالاکی انگشتان | اشتراک زمانی | توجه انتخابی | ترتیب‌دهی به اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی</t>
+          <t>دقت کنترل | درک عمق | هماهنگی چند عضو | بینایی نزدیک | بینایی دور | کنترل نرخ | زمان عکس‌العمل | ثبات دست و بازو | جهت‌گیری پاسخ | حساسیت به مسئله | درک شفاهی | تجسم | سرعت ادراکی | مهارت دستی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی | تشخیص رنگ بصری | قدرت ایستا | مهارت انگشتان | تقسیم توجه | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | پیامد اشتباهات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعداد دفعات تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض آلاینده‌ها | پیامدهای کاری و نتایج سایر کارگران | داخل خودروی روباز یا کار با تجهیزات | سلامت و ایمنی سایر کارگران | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | کار با یا مشارکت در یک گروه یا تیم کاری | فشار زمانی | داخل خودروی کابین‌دار یا کار با تجهیزات کابین‌دار | آزادی در تصمیم‌گیری | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض ارتعاش کل بدن | اهمیت دقیق یا درست بودن کار | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | نزدیکی فیزیکی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | پیامد خطا | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض آلاینده‌ها | پیامدهای کاری و نتایج سایر کارکنان | در یک وسیله نقلیه روباز یا کار با تجهیزات | سلامت و ایمنی سایر کارکنان | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | آزادی در تصمیم‌گیری | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض ارتعاش کل بدن | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | نزدیکی فیزیکی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارگران ساختمانی | اپراتورهای ماشین‌های استخراج مداوم | اپراتورهای جرثقیل و تاورکرین | اپراتورهای لایروب | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و دراگ‌لاین، معدن‌کاری سطحی | دستیاران--کارگران استخراج | کارگران نگهداری بزرگراه‌ها | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای خودروهای صنعتی و تراکتور | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | تعمیرکاران ماشین‌آلات | کارگران نگهداری و تعمیرات، عمومی | نصب‌کنندگان ماشین‌آلات صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتور | اپراتورهای تجهیزات روسازی، زیرسازی و کوبش | اپراتورهای کوبنده شمع | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | دکل‌بندها</t>
+          <t>کارگران ساختمانی | اپراتورهای ماشین استخراج مداوم | اپراتورهای جرثقیل و تاور | اپراتورهای لایروب | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | دستیاران--کارگران استخراج | کارگران نگهداری بزرگراه‌ها | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون صنعتی | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران نگهداری و تعمیرات عمومی | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | اپراتورهای تجهیزات روسازی، زیرسازی و کوبش | اپراتورهای کوبنده شمع | اپراتورهای تجهیزات ریل‌گذاری و نگهداری خطوط آهن | ریگرها</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>نرم‌افزار مدیریت کسب‌وکار | Construction Software Center EasyEst | DevWave Estimate Works | نرم‌افزار بهای تمام‌شده پروژه | Logic Group Scanner Digitizing Software | نرم‌افزار Microsoft Office | Microsoft Windows | Microsoft Word | On Center Quick Bid | Turtle Creek Software Goldenseal | Wilhelm Publishing Threshold</t>
+          <t>نرم‌افزار مدیریت کسب‌وکار | Construction Software Center EasyEst | DevWave Estimate Works | نرم‌افزار هزینه‌یابی کار | Logic Group Scanner Digitizing Software | نرم‌افزار Microsoft Office | Microsoft Windows | Microsoft Word | On Center Quick Bid | Turtle Creek Software Goldenseal | Wilhelm Publishing Threshold</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,22 +798,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | ریاضیات | مکانیک | ایمنی و امنیت عمومی | امور اداری و مدیریت</t>
+          <t>ساختمان و ساخت‌وساز | ریاضیات | مکانیک | ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چالاکی دست | قدرت بالاتنه | انعطاف‌پذیری کششی | بینایی نزدیک | تعادل عمومی بدن | چالاکی انگشتان | قدرت ایستا | تجسم فضایی | بیان شفاهی | درک شفاهی | استقامت بدنی | هماهنگی میان‌اندازه‌ای | دقت کنترل | توجه انتخابی | ترتیب‌دهی به اطلاعات | تشخیص گفتار | بینایی دور | سرعت ادراکی | استدلال قیاسی | حساسیت به مشکلات</t>
+          <t>ثبات دست و بازو | مهارت دستی | قدرت تنه | انعطاف‌پذیری دامنه حرکت | بینایی نزدیک | تعادل کلی بدن | مهارت انگشتان | قدرت ایستا | تجسم | بیان شفاهی | درک شفاهی | استقامت | هماهنگی چند عضو | دقت کنترل | توجه انتخابی | ترتیب‌دهی اطلاعات | تشخیص گفتار | بینایی دور | سرعت ادراکی | استدلال قیاسی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن کار | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای انجام حرکات تکراری | مکالمات تلفنی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | آزادی در تصمیم‌گیری | صرف زمان به صورت پیاده‌روی یا دویدن | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه یا تیم کاری | فشار زمانی | ارتباط با دیگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعداد دفعات تصمیم‌گیری | صرف زمان برای خم کردن یا چرخاندن بدن</t>
+          <t>صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای انجام حرکات تکراری | مکالمات تلفنی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | آزادی در تصمیم‌گیری | صرف زمان برای راه رفتن یا دویدن | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | صرف زمان برای خم کردن یا چرخاندن بدن</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>بناهای آجر و بلوک | نجاران | نصابان موکت | سیمان‌کاران و پرداخت‌کاران بتن | کارگران ساختمانی | کف‌سازان، به جز موکت، چوب و کاشی‌های سخت | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری مکانیکی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | گچ‌کاران و سیمان‌کاران نما | کارگران آرماتوربند و نصب میلگرد | سقف‌سازان | کارگران ورق‌کاری فلزی | کارگران اسکلت فلزی و فولادی ساختمانی | سازندگان و مونتاژکنندگان سازه‌های فلزی | درزگیران دیوار خشک | کارگران و پرداخت‌کاران ترازو | نصابان کاشی و سنگ | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب، به جز اره‌کشی</t>
+          <t>بنّایان آجرکار و بلوک‌کار | نجّاران | نصّابان موکت و فرش | بنّایان سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | گچ‌کاران و بناهای سیمان‌کاری | کارگران آهن تقویتی و میلگرد | سقف‌سازان | کارگران ورق‌کاری | کارگران سازه‌های آهنی و فولادی | سازندگان و مونتاژکاران فلزات سازه‌ای | تپرز | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | انعطاف‌پذیری کششی | قدرت بالاتنه | هماهنگی میان‌اندازه‌ای | چالاکی دست | ثبات دست و بازو | درک شفاهی</t>
+          <t>بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | قدرت تنه | هماهنگی چند عضو | مهارت دستی | ثبات دست و بازو | درک شفاهی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض آلاینده‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | کار با یا مشارکت در یک گروه یا تیم کاری | صرف زمان به صورت پیاده‌روی یا دویدن | سلامت و ایمنی سایر کارگران | قرار گرفتن در معرض ارتفاعات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن کار | مکالمات تلفنی | داخل ساختمان، بدون کنترل شرایط محیطی | صرف زمان برای خم کردن یا چرخاندن بدن | تعداد دفعات تصمیم‌گیری</t>
+          <t>صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض آلاینده‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای راه رفتن یا دویدن | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض ارتفاعات بالا | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | مکالمات تلفنی | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای خم کردن یا چرخاندن بدن | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>بناهای آجر و بلوک | نجاران | سیمان‌کاران و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | کف‌سازان، به جز موکت، چوب و کاشی‌های سخت | ساب‌زن‌ها و پرداخت‌کاران کف | کارگران ساب‌زنی و صیقل‌کاری دستی | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | کارگران عایق‌کاری کف, سقف و دیوار | کارگران عایق‌کاری مکانیکی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | نقاشان، ساختمان و نگهداری | گچ‌کاران و سیمان‌کاران نما | کارگران آرماتوربند و نصب میلگرد | سقف‌سازان | کارگران ورق‌کاری فلزی | کارگران اسکلت فلزی و فولادی ساختمانی | کارگران و پرداخت‌کاران ترازو | نصابان کاشی و سنگ</t>
+          <t>بنّایان آجرکار و بلوک‌کار | نجّاران | بنّایان سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | سنباده‌کاران و پرداخت‌کاران کف | کارگران سنگ‌زنی و پرداخت دستی | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | نقاشان، ساختمان و نگهداری | گچ‌کاران و بناهای سیمان‌کاری | کارگران آهن تقویتی و میلگرد | سقف‌سازان | کارگران ورق‌کاری | کارگران سازه‌های آهنی و فولادی | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | درک مطلب | نظارت | استراتژی‌های یادگیری | ریاضیات | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | درک مطلب | نظارت | راهبردهای یادگیری | ریاضیات | نگارش</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | امور اداری و مدیریت | مکانیک | ریاضیات | طراحی | خدمات مشتریان و پرسنل</t>
+          <t>ساختمان و ساخت‌وساز | مدیریت و اداره | مکانیک | ریاضیات | طراحی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مشکلات | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی به اطلاعات | چالاکی انگشتان | درک شفاهی | ثبات دست و بازو | تشخیص رنگ‌های بصری | انعطاف‌پذیری کششی | قدرت بالاتنه | تجسم فضایی | بیان شفاهی | درک کتبی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | چالاکی دست | بینایی دور | دقت کنترل | توجه انتخابی | استدلال ریاضی | وضوح گفتار | تشخیص گفتار | درک عمق | تعادل عمومی بدن | هماهنگی میان‌اندازه‌ای | سرعت ادراکی | سهولت کار با اعداد | روانی ایده‌ها | بیان کتبی</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | مهارت انگشتان | درک شفاهی | ثبات دست و بازو | تشخیص رنگ بصری | انعطاف‌پذیری دامنه حرکت | قدرت تنه | تجسم | بیان شفاهی | درک کتبی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | مهارت دستی | بینایی دور | دقت کنترل | توجه انتخابی | استدلال ریاضی | وضوح گفتار | تشخیص گفتار | درک عمق | تعادل کلی بدن | هماهنگی چند عضو | سرعت ادراکی | توانایی عددی | روانی ایده‌ها | بیان کتبی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | اهمیت دقیق یا درست بودن کار | صرف زمان برای خم کردن یا چرخاندن بدن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض شرایط خطرناک | صرف زمان به صورت ایستاده | سلامت و ایمنی سایر کارگران | کار با یا مشارکت در یک گروه یا تیم کاری | مکالمات تلفنی | قرار گرفتن در معرض آلاینده‌ها | آزادی در تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، نیش‌ها یا گزیدگی‌ها | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های نامناسب | پیامدهای کاری و نتایج سایر کارگران | صرف زمان برای انجام حرکات تکراری | فشار زمانی | تعداد دفعات تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان به صورت پیاده‌روی یا دویدن | داخل ساختمان، بدون کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض تجهیزات خطرناک | ایمیل | صرف زمان برای حفظ یا بازیافت تعادل | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | فضای باز، زیر سرپناه | صرف زمان به صورت زانو زده، چمباتمه زده، خمیده یا خزیده | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | قرار گرفتن در معرض ارتفاعات | داخل خودروی کابین‌دار یا کار با تجهیزات کابین‌دار</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | اهمیت دقیق یا درست بودن | صرف زمان برای خم کردن یا چرخاندن بدن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض شرایط خطرناک | صرف زمان برای ایستادن | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | قرار گرفتن در معرض آلاینده‌ها | آزادی در تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای انجام حرکات تکراری | فشار زمانی | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای راه رفتن یا دویدن | محیط داخلی، بدون کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض تجهیزات خطرناک | ایمیل | صرف زمان برای حفظ یا بازیابی تعادل | تعامل با مشتریان خارجی یا عموم مردم | فضای باز، زیر سقف | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | قرار گرفتن در معرض ارتفاعات بالا | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | نجاران | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | نصابان و تعمیرکاران خطوط انتقال نیروی برق | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل‌ونقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌ها و رله‌ها | دستیاران--برق‌کاران | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--لوله‌گذاران، لوله‌کش‌ها، نصابان لوله و لوله‌کش‌های بخار | کارگران عایق‌کاری مکانیکی | تکنسین‌های روشنایی | کارگران نگهداری و تعمیرات، عمومی | نصب‌کنندگان ماشین‌آلات صنعتی | لوله‌کش‌ها، نصابان لوله و لوله‌کش‌های بخار | کارگران ورق‌کاری فلزی | نصابان سیستم‌های خورشیدی فتوولتائیک | کارگران اسکلت فلزی و فولادی ساختمانی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | نجّاران | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصابان و تعمیرکاران خطوط انتقال نیروی برق | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | دستیاران--برق‌کاران | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کارگران عایق‌کاری، مکانیکی | تکنسین‌های نورپردازی | کارگران نگهداری و تعمیرات عمومی | مهندسان نصب ماشین‌آلات | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | کارگران ورق‌کاری | نصابان سیستم‌های فتوولتائیک خورشیدی | کارگران سازه‌های آهنی و فولادی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -969,22 +969,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | مکانیک | ریاضیات | امور اداری و مدیریت | طراحی | خدمات مشتریان و پرسنل</t>
+          <t>ساختمان و ساخت‌وساز | مکانیک | ریاضیات | مدیریت و اداره | طراحی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | بینایی نزدیک | قدرت بالاتنه | هماهنگی میان‌اندازه‌ای | چالاکی دست | حساسیت به مشکلات | ترتیب‌دهی به اطلاعات | قدرت ایستا | دقت کنترل | وضوح گفتار | تشخیص گفتار | بینایی دور | تعادل عمومی بدن | انعطاف‌پذیری کششی | چالاکی انگشتان | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | درک کتبی | درک شفاهی</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | قدرت تنه | هماهنگی چند عضو | مهارت دستی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | قدرت ایستا | دقت کنترل | وضوح گفتار | تشخیص گفتار | بینایی دور | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | مهارت انگشتان | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | درک کتبی | درک شفاهی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | اهمیت دقیق یا درست بودن کار | ارتباط با دیگران | کار با یا مشارکت در یک گروه یا تیم کاری | صرف زمان به صورت ایستاده | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعداد دفعات تصمیم‌گیری | آزادی در تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامدهای کاری و نتایج سایر کارگران | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارگران | داخل ساختمان، بدون کنترل شرایط محیطی | پیامد اشتباهات | فضای باز، زیر سرپناه | قرار گرفتن در معرض ارتفاعات | مکالمات تلفنی | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | اهمیت دقیق یا درست بودن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای ایستادن | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامدهای کاری و نتایج سایر کارکنان | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | محیط داخلی، بدون کنترل شرایط محیطی | پیامد خطا | فضای باز، زیر سقف | قرار گرفتن در معرض ارتفاعات بالا | مکالمات تلفنی | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>نصابان و تعمیرکاران شیشه خودرو | بناهای آجر و بلوک | کابینت‌سازان و نجاران کارگاهی | نجاران | نصابان دیوار خشک و تایل سقف | کف‌سازان، به جز موکت، چوب و کاشی‌های سخت | پرداخت‌کاران مبلمان | شیشه‌دمان، قالب‌ریزان، خم‌کنندگان و پرداخت‌کاران شیشه | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری مکانیکی | تعمیرکاران درهای مکانیکی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | گچ‌کاران و سیمان‌کاران نما | سقف‌سازان | کارگران ورق‌کاری فلزی | کارگران اسکلت فلزی و فولادی ساختمانی | سازندگان و مونتاژکنندگان سازه‌های فلزی | کارگران و پرداخت‌کاران ترازو | نصابان کاشی و سنگ</t>
+          <t>نصب‌کنندگان و تعمیرکنندگان شیشه خودرو | بنّایان آجرکار و بلوک‌کار | کابینت‌سازان و نجاران نیمکت | نجّاران | نصابان دیوار خشک و تایل سقف | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | پرداخت‌کاران مبلمان | شیشه‌گران، قالب‌سازان، خم‌کاران و پرداخت‌کاران شیشه | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | کارگران عایق‌کاری کف، سقف و دیوار | کارگران عایق‌کاری، مکانیکی | تعمیرکاران درب‌های مکانیکی | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | گچ‌کاران و بناهای سیمان‌کاری | سقف‌سازان | کارگران ورق‌کاری | کارگران سازه‌های آهنی و فولادی | سازندگان و مونتاژکاران فلزات سازه‌ای | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1026,22 +1026,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ساختمان و ساخت‌وساز | خدمات مشتریان و پرسنل | مکانیک</t>
+          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | مکانیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>انعطاف‌پذیری کششی | هماهنگی میان‌اندازه‌ای | چالاکی دست | تعادل عمومی بدن | قدرت بالاتنه | ثبات دست و بازو | دقت کنترل | تجسم فضایی | وضوح گفتار | درک عمق | بینایی نزدیک | استقامت بدنی | قدرت ایستا | چالاکی انگشتان | توجه انتخابی | بیان شفاهی</t>
+          <t>انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | مهارت دستی | تعادل کلی بدن | قدرت تنه | ثبات دست و بازو | دقت کنترل | تجسم | وضوح گفتار | درک عمق | بینایی نزدیک | استقامت | قدرت ایستا | مهارت انگشتان | توجه انتخابی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>صرف زمان به صورت ایستاده | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه یا تیم کاری | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، نیش‌ها یا گزیدگی‌ها | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | داخل ساختمان، بدون کنترل شرایط محیطی | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های نامناسب | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | ارتباط با دیگران | قرار گرفتن در معرض ارتفاعات | داخل خودروی کابین‌دار یا کار با تجهیزات کابین‌دار | تعداد دفعات تصمیم‌گیری | مکالمات تلفنی | سلامت و ایمنی سایر کارگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>صرف زمان برای ایستادن | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | ارتباط با دیگران | قرار گرفتن در معرض ارتفاعات بالا | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فراوانی تصمیم‌گیری | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>بناهای آجر و بلوک | نجاران | نصابان موکت | سیمان‌کاران و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | لمینت‌کاران و سازندگان فایبرگلاس | کف‌سازان، به جز موکت، چوب و کاشی‌های سخت | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--لوله‌گذاران، لوله‌کش‌ها، نصابان لوله و لوله‌کش‌های بخار | کارگران عایق‌کاری مکانیکی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | لوله‌گذاران | گچ‌کاران و سیمان‌کاران نما | لوله‌کش‌ها، نصابان لوله و لوله‌کش‌های بخار | سقف‌سازان | کارگران ورق‌کاری فلزی | نصابان و تکنسین‌های سیستم‌های حرارتی خورشیدی | درزگیران دیوار خشک | نصابان کاشی و سنگ</t>
+          <t>بنّایان آجرکار و بلوک‌کار | نجّاران | نصّابان موکت و فرش | بنّایان سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار خشک و تایل سقف | لمینت‌کاران و سازندگان فایبرگلاس | کفپوش‌کاران، به‌جز موکت، چوب و کاشی سخت | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کارگران عایق‌کاری، مکانیکی | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | لوله‌گذاران | گچ‌کاران و بناهای سیمان‌کاری | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | سقف‌سازان | کارگران ورق‌کاری | نصابان و تکنسین‌های حرارتی خورشیدی | تپرز | کاشی‌کاران و سنگ‌کاران</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0073_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0073_fa.xlsx
@@ -503,22 +503,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CPR International GeneralCOST Estimator | CPR Visual Estimator | ProEst | Intuit QuickBooks | Microsoft Excel | Microsoft Windows | On Center Quick Bid | Sapro Systems Paymee</t>
+          <t>CPR International GeneralCOST Estimator | CPR Visual Estimator | نرم‌افزار مدیریت ساخت ProEst | Intuit QuickBooks | Microsoft Excel | Microsoft Windows | On Center Quick Bid | Sapro Systems Paymee</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | ریاضیات</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ساخت و ساز | طراحی | ریاضیات | زبان انگلیسی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | شیمی | مکانیک | ایمنی و امنیت عمومی</t>
+          <t>ساختمان و ساخت‌وساز | طراحی | ریاضیات | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی | شیمی | مکانیک | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>چابکی دستی | دید نزدیک | قدرت بالاتنه | هماهنگی میان‌اعضا | ثبات دست و بازو | دید دور | چابکی انگشتان | انعطاف‌پذیری بدنی | استقامت بدنی | قدرت ایستا | کنترل دقیق | تجسم فضایی | حساسیت به مسئله | تشخیص رنگ‌های بصری | قدرت پویا | توجه انتخابی | مرتب‌سازی اطلاعات</t>
+          <t>مهارت دستی | بینایی نزدیک | قدرت تنه | هماهنگی چند عضو | ثبات دست و بازو | بینایی دور | مهارت انگشتان | انعطاف‌پذیری دامنه حرکت | استقامت | قدرت ایستا | دقت کنترل | تجسم | حساسیت به مسئله | تشخیص رنگ بصری | قدرت پویا | توجه انتخابی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>بناهای آجرکار و بلوک‌کار | نجاران | نصابان موکت | سیمان‌کاران و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | نصابان کفپوش (به‌جز موکت و چوب) | ساب‌زنان و پرداخت‌کاران کف | قالب‌ریزان و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران مبلمان و چوب | پرداخت‌کاران دستی و ساب‌زنان دستی | کمک‌بناهای آجرکار، بلوک‌کار، سنگ‌کار و کاشی‌کار | عایق‌کاران کف، سقف و دیوار | قالب‌ریزان و شکل‌دهندگان (به‌جز فلز و پلاستیک) | گچ‌کاران و سیمان‌کاران نما | تعمیرکاران مواد نسوز | سنگ‌فرش‌کاران | برش‌کاران و تراش‌کاران سنگ | سنگ‌تراشان | کاشی‌کاران و سنگ‌کاران</t>
+          <t>بنایان و سفت‌کاران ساختمان | نجاران و درودگران | موکت‌کاران و نصابان فرش | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | ساب‌زنان و پرداخت‌کاران کف | قالب‌گیران و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | عایق‌کاران کف، سقف و دیوار | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | سفیدکاران و گچ‌کاران نما | تعمیرکاران و نسوزکاران مواد دیرگداز صنعتی | سنگ‌فرش‌کاران و موزاییک‌ریزان قطعه‌ای | سنگ‌تراشان و حکاکان صنعتی سنگ | سنگ‌کاران ساختمانی | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,22 +560,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Autodesk Revit | Microsoft Excel | Microsoft Office | Microsoft Outlook | Microsoft Windows | Microsoft Word | Oracle Primavera</t>
+          <t>Autodesk Revit | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Windows | Microsoft Word | Oracle Primavera</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ساخت و ساز | ایمنی و امنیت عمومی | مکانیک</t>
+          <t>ساختمان و ساخت‌وساز | ایمنی و امنیت عمومی | مکانیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>چابکی دستی | قدرت ایستا | هماهنگی میان‌اعضا | ثبات دست و بازو | درک شفاهی | بیان شفاهی | حساسیت به مسئله | کنترل دقیق | قدرت بالاتنه | دید نزدیک | دید دور | انعطاف‌پذیری بدنی | استقامت بدنی | قدرت پویا | چابکی انگشتان | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | درک عمق | کنترل سرعت | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی</t>
+          <t>مهارت دستی | قدرت ایستا | هماهنگی چند عضو | ثبات دست و بازو | درک شفاهی | بیان شفاهی | حساسیت به مسئله | دقت کنترل | قدرت تنه | بینایی نزدیک | بینایی دور | انعطاف‌پذیری دامنه حرکت | استقامت | قدرت پویا | مهارت انگشتان | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | درک عمق | کنترل نرخ | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>بناهای آجرکار و بلوک‌کار | نجاران | سیمان‌کاران و پرداخت‌کاران بتن | نصابان دیوار کاذب و تایل سقف | اپراتورهای ماشین‌های حفاری و بارگیری | پرداخت‌کاران دستی و ساب‌زنان دستی | کمک‌بناهای آجرکار، بلوک‌کار، سنگ‌کار و کاشی‌کار | اپراتورهای بالابر و وینچ | عایق‌کاران کف, سقف و دیوار | تغذیه‌کنندگان ماشین‌آلات ساختمانی | تعمیرکاران ماشین‌آلات | قالب‌ریزان و شکل‌دهندگان (به‌جز فلز و پلاستیک) | اپراتورهای ماشین‌آلات سنگین راهسازی | اپراتورهای تجهیزات آسفالت‌ریزی و کوبش | لوله‌گذاران | لوله‌کشان و تاسیسات‌کاران | سنگ‌فرش‌کاران | کانال‌سازان و ورق‌کاران | اسکلت‌کاران فلزی | اپراتورهای ماشین‌آلات صنایع چوب</t>
+          <t>بنایان و سفت‌کاران ساختمان | نجاران و درودگران | بتن‌ریزان و پرداخت‌کاران بتن | نصابان دیوار کاذب و تایل سقف | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | اپراتورهای بالابر و وینچ | عایق‌کاران کف، سقف و دیوار | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای تجهیزات آسفالت‌ریزی، پخش و کوبش | لوله‌گذاران خطوط انتقال | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | سنگ‌فرش‌کاران و موزاییک‌ریزان قطعه‌ای | کارگران ورق‌کاری فلزی | اسکلت‌سازان و نصابان سازه‌های فولادی | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD Civil 3D | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | HCSS HeavyBid | Microsoft Excel | Microsoft Office | Microsoft Outlook | نرم‌افزار ثبت کارکرد | نرم‌افزار مدیریت انبار WMS</t>
+          <t>Autodesk AutoCAD Civil 3D | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | HCSS HeavyBid | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | نرم‌افزار ثبت کارکرد | سیستم مدیریت انبار WMS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -627,12 +627,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ساخت و ساز | مکانیک</t>
+          <t>ساختمان و ساخت‌وساز | مکانیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>کنترل دقیق | حساسیت به مسئله | هماهنگی میان‌اعضا | کنترل سرعت | زمان عکس‌العمل | دید دور | قدرت بالاتنه | قدرت ایستا | وضوح گفتار | تشخیص گفتار | درک عمق | ثبات دست و بازو | توجه انتخابی | تجسم فضایی | مرتب‌سازی اطلاعات | استدلال قیاسی | بیان شفاهی | درک شفاهی | انعطاف‌پذیری بدنی | جهت‌یابی پاسخ | چابکی دستی</t>
+          <t>دقت کنترل | حساسیت به مسئله | هماهنگی چند عضو | کنترل نرخ | زمان عکس‌العمل | بینایی دور | قدرت تنه | قدرت ایستا | وضوح گفتار | تشخیص گفتار | درک عمق | ثبات دست و بازو | توجه انتخابی | تجسم | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان شفاهی | درک شفاهی | انعطاف‌پذیری دامنه حرکت | جهت‌گیری پاسخ | مهارت دستی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>سیمان‌کاران و پرداخت‌کاران بتن | کارگران ساختمانی | اپراتورهای ماشین‌آلات استخراج معدن | حفاران زمین (به‌جز نفت و گاز) | اپراتورهای ماشین‌های حفاری و بارگیری | پرداخت‌کاران دستی و ساب‌زنان دستی | راهداران و کارگران نگهداری راه‌ها | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | تعمیرکاران ماشین‌آلات | نصابان ماشین‌آلات صنعتی | مکانیک‌های ماشین‌آلات سنگین | اپراتورهای ماشین‌آلات سنگین راهسازی | اپراتورهای شمع‌کوب | لوله‌گذاران | کارگران نگهداری خطوط راه‌آهن | کارگران فنی سکوهای نفتی | سنگ‌فرش‌کاران | موزاییک‌کاران و پرداخت‌کاران terrazzo | اپراتورهای ماشین‌آلات صنایع چوب</t>
+          <t>بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | اپراتورهای ماشین‌های استخراج پیوسته | حفاران زمین، به‌جز نفت و گاز | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | کارگران راهداری و نگهداری جاده‌ها | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای دستگاه شمع‌کوب | لوله‌گذاران خطوط انتقال | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | کارگران عمومی سکو و میادین نفت و گاز | سنگ‌فرش‌کاران و موزاییک‌ریزان قطعه‌ای | موزاییک‌کاران و پرداخت‌کاران terrazzo | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>نرم‌افزار ایمیل | GRLWEAP | نرم‌افزار GPS | Microsoft Excel | CAPWAP | PDA</t>
+          <t>نرم‌افزار ایمیل | GRLWEAP | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Microsoft Excel | CAPWAP | PDA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال</t>
+          <t>نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ساخت و ساز | مکانیک | ریاضیات | حمل و نقل | مهندسی و فناوری | ایمنی و امنیت عمومی | طراحی</t>
+          <t>ساختمان و ساخت‌وساز | مکانیک | ریاضیات | حمل و نقل | مهندسی و فناوری | ایمنی و امنیت عمومی | طراحی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>کنترل دقیق | درک عمق | هماهنگی میان‌اعضا | زمان عکس‌العمل | چابکی دستی | حساسیت به مسئله | کنترل سرعت | جهت‌یابی پاسخ | توجه انتخابی | ثبات دست و بازو | استدلال قیاسی | تشخیص گفتار | دید دور | تجسم فضایی | توجه شنیداری | دید نزدیک | چابکی انگستان | جهت‌یابی فضایی | مرتب‌سازی اطلاعات | استدلال استقرایی | بیان شفاهی | درک شفاهی</t>
+          <t>دقت کنترل | درک عمق | هماهنگی چند عضو | زمان عکس‌العمل | مهارت دستی | حساسیت به مسئله | کنترل نرخ | جهت‌گیری پاسخ | توجه انتخابی | ثبات دست و بازو | استدلال قیاسی | تشخیص گفتار | بینایی دور | تجسم | توجه شنیداری | بینایی نزدیک | مهارت انگشتان | جهت‌گیری فضایی | ترتیب‌دهی اطلاعات | استدلال استقرایی | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مکانیک‌های خودروهای سنگین و دیزل | کارگران ساختمانی | اپراتورهای ماشین‌آلات استخراج معدن | اپراتورهای جرثقیل و تاورکرین | حفاران زمین (به‌جز نفت و گاز) | اپراتورهای ماشین‌های حفاری و بارگیری | راهداران و کارگران نگهداری راه‌ها | اپراتورهای بالابر و وینچ | رانندگان لیفتراک و تراکتورهای صنعتی | اپراتورهای ماشین‌آلات بارگیری معدن زیرزمینی | تعمیرکاران ماشین‌آلات | نصابان ماشین‌آلات صنعتی | مکانیک‌های ماشین‌آلات سنگین | اپراتورهای ماشین‌آلات سنگین راهسازی | اپراتورهای تجهیزات آسفالت‌ریزی و کوبش | تعمیرکاران واگن‌های قطار | کارگران نگهداری خطوط راه‌آهن | دکل‌بندها | کارگران فنی سکوهای نفتی | اسکلت‌کاران فلزی</t>
+          <t>مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | کارگران ساختمانی | اپراتورهای ماشین‌های استخراج پیوسته | اپراتورهای جرثقیل و تاورکرین | حفاران زمین، به‌جز نفت و گاز | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | کارگران راهداری و نگهداری جاده‌ها | اپراتورهای بالابر و وینچ | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | کارگران تعمیر و نگهداری ماشین‌آلات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای تجهیزات آسفالت‌ریزی، پخش و کوبش | تعمیرکار واگن قطار | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | کارگران عمومی سکو و میادین نفت و گاز | اسکلت‌سازان و نصابان سازه‌های فولادی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزار ثبت تعمیرات | Microsoft Excel | Microsoft Office | Microsoft Outlook | Microsoft Windows | نرم‌افزار ثبت کارکرد</t>
+          <t>نرم‌افزار ثبت تعمیر و نگهداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Windows | نرم‌افزار ثبت کارکرد</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال</t>
+          <t>نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>کنترل دقیق | درک عمق | هماهنگی میان‌اعضا | دید نزدیک | دید دور | کنترل سرعت | زمان عکس‌العمل | ثبات دست و بازو | جهت‌یابی پاسخ | حساسیت به مسئله | درک شفاهی | تجسم فضایی | سرعت ادراکی | چابکی دستی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی | تشخیص رنگ‌های بصری | قدرت ایستا | چابکی انگشتان | تقسیم توجه | توجه انتخابی | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی</t>
+          <t>دقت کنترل | درک عمق | هماهنگی چند عضو | بینایی نزدیک | بینایی دور | کنترل نرخ | زمان عکس‌العمل | ثبات دست و بازو | جهت‌گیری پاسخ | حساسیت به مسئله | درک شفاهی | تجسم | سرعت ادراکی | مهارت دستی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی | تشخیص رنگ بصری | قدرت ایستا | مهارت انگشتان | تقسیم توجه | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارگران ساختمانی | اپراتورهای ماشین‌آلات استخراج معدن | اپراتورهای جرثقیل و تاورکرین | اپراتورهای لایروب | حفاران زمین (به‌جز نفت و گاز) | اپراتورهای ماشین‌های حفاری و بارگیری | کمک‌کارگران بخش استخراج | راهداران و کارگران نگهداری راه‌ها | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | رانندگان لیفتراک و تراکتورهای صنعتی | اپراتورهای ماشین‌آلات بارگیری معدن زیرزمینی | تعمیرکاران ماشین‌آلات | تعمیرکاران عمومی | نصابان ماشین‌آلات صنعتی | مکانیک‌های ماشین‌آلات سنگین | اپراتورهای تجهیزات آسفالت‌ریزی و کوبش | اپراتورهای شمع‌کوب | کارگران نگهداری خطوط راه‌آهن | دکل‌بندها</t>
+          <t>کارگران ساختمانی | اپراتورهای ماشین‌های استخراج پیوسته | اپراتورهای جرثقیل و تاورکرین | اپراتورهای لایروب | حفاران زمین، به‌جز نفت و گاز | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | کارگران کمکی استخراج معدن | کارگران راهداری و نگهداری جاده‌ها | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران عمومی تعمیرات و نگهداری تاسیسات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | اپراتورهای تجهیزات آسفالت‌ریزی، پخش و کوبش | اپراتورهای دستگاه شمع‌کوب | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ساخت و ساز | ریاضیات | مکانیک | ایمنی و امنیت عمومی | مدیریت و امور اداری</t>
+          <t>ساختمان و ساخت‌وساز | ریاضیات | مکانیک | ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی دستی | قدرت بالاتنه | انعطاف‌پذیری بدنی | دید نزدیک | حفظ تعادل بدنی | چابکی انگشتان | قدرت ایستا | تجسم فضایی | بیان شفاهی | درک شفاهی | استقامت بدنی | هماهنگی میان‌اعضا | کنترل دقیق | توجه انتخابی | مرتب‌سازی اطلاعات | تشخیص گفتار | دید دور | سرعت ادراکی | استدلال قیاسی | حساسیت به مسئله</t>
+          <t>ثبات دست و بازو | مهارت دستی | قدرت تنه | انعطاف‌پذیری دامنه حرکت | بینایی نزدیک | تعادل کلی بدن | مهارت انگشتان | قدرت ایستا | تجسم | بیان شفاهی | درک شفاهی | استقامت | هماهنگی چند عضو | دقت کنترل | توجه انتخابی | ترتیب‌دهی اطلاعات | تشخیص گفتار | بینایی دور | سرعت ادراکی | استدلال قیاسی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>بناهای آجرکار و بلوک‌کار | نجاران | نصابان موکت | سیمان‌کاران و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان کفپوش (به‌جز موکت و چوب) | کمک‌بناهای آجرکار، بلوک‌کار، سنگ‌کار و کاشی‌کار | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات | قالب‌ریزان و شکل‌دهندگان (به‌جز فلز و پلاستیک) | گچ‌کاران و سیمان‌کاران نما | آرماتوربندان | سقف‌سازان و عایق‌کاران رطوبتی | کانال‌سازان و ورق‌کاران | اسکلت‌کاران فلزی | مونتاژکاران سازه‌های فلزی | بتونه‌کاران و درزگیران دیوار کاذب | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران | اپراتورهای ماشین‌آلات صنایع چوب</t>
+          <t>بنایان و سفت‌کاران ساختمان | نجاران و درودگران | موکت‌کاران و نصابان فرش | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | سفیدکاران و گچ‌کاران نما | آرماتوربندان و نصابان میلگرد | عایق‌کاران و نصابان پوشش‌های سقفی | کارگران ورق‌کاری فلزی | اسکلت‌سازان و نصابان سازه‌های فولادی | سازندگان و مونتاژکاران سازه‌های فلزی | بتونه‌کاران و درزگیران دیوار کاذب | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران ظریف | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,22 +845,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JOBPOWER | EasyEst | Estimate Works | Intuit QuickBooks | Microsoft Dynamics | Microsoft Office | On Center Quick Bid | Goldenseal</t>
+          <t>JOBPOWER | EasyEst | Estimate Works | Intuit QuickBooks | Microsoft Dynamics | نرم‌افزار Microsoft Office | On Center Quick Bid | Goldenseal</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | ریاضیات</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ساخت و ساز</t>
+          <t>ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | انعطاف‌پذیری بدنی | قدرت بالاتنه | هماهنگی میان‌اعضا | چابکی دستی | ثبات دست و بازو | درک شفاهی</t>
+          <t>بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | قدرت تنه | هماهنگی چند عضو | مهارت دستی | ثبات دست و بازو | درک شفاهی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>بناهای آجرکار و بلوک‌کار | نجاران | سیمان‌کاران و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | نصابان کفپوش (به‌جز موکت و چوب) | ساب‌زنان و پرداخت‌کاران کف | پرداخت‌کاران دستی و ساب‌زنان دستی | کمک‌بناهای آجرکار، بلوک‌کار، سنگ‌کار و کاشی‌کار | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات | قالب‌ریزان و شکل‌دهندگان (به‌جز فلز و پلاستیک) | نقاشان ساختمان | گچ‌کاران و سیمان‌کاران نما | آرماتوربندان | سقف‌سازان و عایق‌کاران رطوبتی | کانال‌سازان و ورق‌کاران | اسکلت‌کاران فلزی | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران</t>
+          <t>بنایان و سفت‌کاران ساختمان | نجاران و درودگران | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | ساب‌زنان و پرداخت‌کاران کف | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | نقاشان ساختمان و تاسیسات | سفیدکاران و گچ‌کاران نما | آرماتوربندان و نصابان میلگرد | عایق‌کاران و نصابان پوشش‌های سقفی | کارگران ورق‌کاری فلزی | اسکلت‌سازان و نصابان سازه‌های فولادی | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | درک مطلب | نظارت | راهبردهای یادگیری | ریاضیات | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | درک مطلب | نظارت | راهبردهای یادگیری | ریاضیات | نگارش</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ساخت و ساز | مدیریت و امور اداری | مکانیک | ریاضیات | طراحی | خدمات مشتریان و خدمات فردی</t>
+          <t>ساختمان و ساخت‌وساز | مدیریت و اداره | مکانیک | ریاضیات | طراحی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | چابکی انگشتان | درک شفاهی | ثبات دست و بازو | تشخیص رنگ‌های بصری | انعطاف‌پذیری بدنی | قدرت بالاتنه | تجسم فضایی | بیان شفاهی | درک کتبی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | چابکی دستی | دید دور | کنترل دقیق | توجه انتخابی | استدلال ریاضی | وضوح گفتار | تشخیص گفتار | درک عمق | حفظ تعادل بدنی | هماهنگی میان‌اعضا | سرعت ادراکی | سهولت کار با اعداد | روان بودن ایده‌ها | بیان کتبی</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | مهارت انگشتان | درک شفاهی | ثبات دست و بازو | تشخیص رنگ بصری | انعطاف‌پذیری دامنه حرکت | قدرت تنه | تجسم | بیان شفاهی | درک کتبی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | مهارت دستی | بینایی دور | دقت کنترل | توجه انتخابی | استدلال ریاضی | وضوح گفتار | تشخیص گفتار | درک عمق | تعادل کلی بدن | هماهنگی چند عضو | سرعت ادراکی | توانایی عددی | روانی ایده‌ها | بیان کتبی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مونتاژکاران بدنه و سیستم‌های هواپیما | دیگ‌سازان | نجاران | تعمیرکاران الکتروموتور و ابزارهای برقی | سیم‌کشان و ماموران تعمیرات خطوط انتقال نیرو | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | تعمیرکاران تجهیزات الکتریکی ناوگان حمل و نقل | تعمیرکاران تجهیزات الکتریکی صنعتی و تجاری | تعمیرکاران پست‌های برق و رله‌ها | کمک‌برق‌کاران | کمک‌کارگران نصب، تعمیر و نگهداری | کمک‌لوله‌کشان و تاسیسات‌کاران | عایق‌کاران تاسیسات | تکنسین‌های نورپردازی | تعمیرکاران عمومی | نصابان ماشین‌آلات صنعتی | لوله‌کشان و تاسیسات‌کاران | کانال‌سازان و ورق‌کاران | نصابان سیستم‌های خورشیدی فتوولتاییک | اسکلت‌کاران فلزی</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان و مخزن‌سازان صنعتی | نجاران و درودگران | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | کمک‌برق‌کاران | کارگران کمکی نصب، نگهداری و تعمیرات | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | عایق‌کاران تاسیسات مکانیکی | تکنسین‌های نورپردازی | کارگران عمومی تعمیرات و نگهداری تاسیسات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | کارگران ورق‌کاری فلزی | نصابان سیستم‌های خورشیدی فتوولتائیک | اسکلت‌سازان و نصابان سازه‌های فولادی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>American Glazing Software AGS WindowPricer | BidMaster | D-CALC FACADE 4000 | Microsoft Excel | Microsoft Office | Microsoft Windows | نرم‌افزار دستور کار</t>
+          <t>American Glazing Software AGS WindowPricer | BidMaster | D-CALC FACADE 4000 | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Windows | نرم‌افزار دستور کار</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ساخت و ساز | مکانیک | ریاضیات | مدیریت و امور اداری | طراحی | خدمات مشتریان و خدمات فردی</t>
+          <t>ساختمان و ساخت‌وساز | مکانیک | ریاضیات | مدیریت و اداره | طراحی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دید نزدیک | قدرت بالاتنه | هماهنگی میان‌اعضا | چابکی دستی | حساسیت به مسئله | مرتب‌سازی اطلاعات | قدرت ایستا | کنترل دقیق | وضوح گفتار | تشخیص گفتار | دید دور | حفظ تعادل بدنی | انعطاف‌پذیری بدنی | چابکی انگشتان | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | درک کتبی | درک شفاهی</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | قدرت تنه | هماهنگی چند عضو | مهارت دستی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | قدرت ایستا | دقت کنترل | وضوح گفتار | تشخیص گفتار | بینایی دور | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | مهارت انگشتان | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | درک کتبی | درک شفاهی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>نصابان و تعمیرکاران شیشه خودرو | بناهای آجرکار و بلوک‌کار | کابینت‌سازان | نجاران | نصابان دیوار کاذب و تایل سقف | نصابان کفپوش (به‌جز موکت و چوب) | پرداخت‌کاران مبلمان و چوب | شیشه‌گران و شکل‌دهندگان شیشه | کمک‌بناهای آجرکار، بلوک‌کار، سنگ‌کار و کاشی‌کار | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات | تعمیرکاران درهای اتوماتیک و مکانیکی | قالب‌ریزان و شکل‌دهندگان (به‌جز فلز و پلاستیک) | گچ‌کاران و سیمان‌کاران نما | سقف‌سازان و عایق‌کاران رطوبتی | کانال‌سازان و ورق‌کاران | اسکلت‌کاران فلزی | مونتاژکاران سازه‌های فلزی | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران</t>
+          <t>نصاب و تعمیرکار شیشه خودرو | بنایان و سفت‌کاران ساختمان | کابینت‌سازان و نجاران کارگاهی | نجاران و درودگران | نصابان دیوار کاذب و تایل سقف | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | دمندگان، قالب‌گیران، خم‌کاران و پرداخت‌کاران شیشه | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | عایق‌کاران کف، سقف و دیوار | عایق‌کاران تاسیسات مکانیکی | تعمیرکاران درب‌های مکانیکی و اتوماتیک | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | سفیدکاران و گچ‌کاران نما | عایق‌کاران و نصابان پوشش‌های سقفی | کارگران ورق‌کاری فلزی | اسکلت‌سازان و نصابان سازه‌های فولادی | سازندگان و مونتاژکاران سازه‌های فلزی | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,22 +1016,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CMSN FieldPAK | Comput-Ability Mechanical Insulation Key Estimator | Microsoft Excel | Microsoft Office | Microsoft Outlook | Microsoft Windows | NAIMA 3E Plus | Goldenseal</t>
+          <t>CMSN FieldPAK | Comput-Ability Mechanical Insulation Key Estimator | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Windows | NAIMA 3E Plus | Goldenseal</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ساخت و ساز | خدمات مشتریان و خدمات فردی | مکانیک</t>
+          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | مکانیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>انعطاف‌پذیری بدنی | هماهنگی میان‌اعضا | چابکی دستی | حفظ تعادل بدنی | قدرت بالاتنه | ثبات دست و بازو | کنترل دقیق | تجسم فضایی | وضوح گفتار | درک عمق | دید نزدیک | استقامت بدنی | قدرت ایستا | چابکی انگشتان | توجه انتخابی | بیان شفاهی</t>
+          <t>انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | مهارت دستی | تعادل کلی بدن | قدرت تنه | ثبات دست و بازو | دقت کنترل | تجسم | وضوح گفتار | درک عمق | بینایی نزدیک | استقامت | قدرت ایستا | مهارت انگشتان | توجه انتخابی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>بناهای آجرکار و بلوک‌کار | نجاران | نصابان موکت | سیمان‌کاران و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | لمینت‌کاران فایبرگلاس | نصابان کفپوش (به‌جز موکت و چوب) | کمک‌بناهای آجرکار، بلوک‌کار، سنگ‌کار و کاشی‌کار | کمک‌لوله‌کشان و تاسیسات‌کاران | عایق‌کاران تاسیسات | قالب‌ریزان و شکل‌دهندگان (به‌جز فلز و پلاستیک) | لوله‌گذاران | گچ‌کاران و سیمان‌کاران نما | لوله‌کشان و تاسیسات‌کاران | سقف‌سازان و عایق‌کاران رطوبتی | کانال‌سازان و ورق‌کاران | تکنسین‌های سیستم‌های خورشیدی حرارتی | بتونه‌کاران و درزگیران دیوار کاذب | کاشی‌کاران و سنگ‌کاران</t>
+          <t>بنایان و سفت‌کاران ساختمان | نجاران و درودگران | موکت‌کاران و نصابان فرش | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | لایه‌نشانان و سازندگان فایبرگلاس | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | عایق‌کاران تاسیسات مکانیکی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | لوله‌گذاران خطوط انتقال | سفیدکاران و گچ‌کاران نما | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | عایق‌کاران و نصابان پوشش‌های سقفی | کارگران ورق‌کاری فلزی | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی | بتونه‌کاران و درزگیران دیوار کاذب | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
